--- a/_files/projecao_gastos/6. ETA ETE BIO - Previsão de Gastos 2025 e 2026.xlsx
+++ b/_files/projecao_gastos/6. ETA ETE BIO - Previsão de Gastos 2025 e 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\_files\projecao_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD145A6-BC33-4533-9D69-1781003B304F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEFA6FA-0B4F-4C79-9BFE-FD9C230F0CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{093689EF-D701-4890-B8A9-8BD8B50DC7E2}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>Status</t>
   </si>
@@ -247,13 +247,7 @@
     <t>FORNECEDOR ETA TESTE</t>
   </si>
   <si>
-    <t>SERVIÇO TESTE 1</t>
-  </si>
-  <si>
-    <t>SERVIÇO TESTE 2</t>
-  </si>
-  <si>
-    <t>SERVIÇO TESTE 3</t>
+    <t>COMPRA MATERIAL</t>
   </si>
 </sst>
 </file>
@@ -14252,9 +14246,7 @@
       <c r="D2" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="48" t="s">
-        <v>63</v>
-      </c>
+      <c r="E2" s="48"/>
       <c r="F2" s="53">
         <v>8000</v>
       </c>
@@ -14289,9 +14281,7 @@
       <c r="D3" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="48" t="s">
-        <v>64</v>
-      </c>
+      <c r="E3" s="48"/>
       <c r="F3" s="53">
         <v>8000</v>
       </c>
@@ -14326,9 +14316,7 @@
       <c r="D4" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="48" t="s">
-        <v>65</v>
-      </c>
+      <c r="E4" s="48"/>
       <c r="F4" s="53">
         <v>8000</v>
       </c>
@@ -14358,9 +14346,15 @@
       <c r="C5" s="43"/>
       <c r="D5" s="40"/>
       <c r="E5" s="49"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="13"/>
+      <c r="F5" s="53">
+        <v>250000</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="13">
+        <v>242</v>
+      </c>
       <c r="I5" s="13"/>
       <c r="J5" s="40"/>
       <c r="K5" s="13"/>
@@ -14385,7 +14379,9 @@
       <c r="G6" s="45"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
-      <c r="J6" s="40"/>
+      <c r="J6" s="40" t="s">
+        <v>63</v>
+      </c>
       <c r="K6" s="13"/>
       <c r="L6" s="15"/>
       <c r="M6" s="11"/>
@@ -25877,25 +25873,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010071220A11FEA46C4886D3604CC483AD6B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bb07fbe832bfbac930195f44faefcab7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2" xmlns:ns3="8de5c96d-c68a-4bc1-8ca7-a6766c74fd4d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71ce47b93599878504e7d9a94c5299da" ns2:_="" ns3:_="">
     <xsd:import namespace="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
@@ -26124,25 +26101,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C5C945-474E-4133-9AF8-55A4124AD51D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26159,4 +26137,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDA4EE2-72BB-4CD5-80FF-EAFC698EEABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60843E7F-DCA1-4FBE-8AEE-F739F63FAD5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>